--- a/Result/checksun_f/2025-09-06.xlsx
+++ b/Result/checksun_f/2025-09-06.xlsx
@@ -486,157 +486,157 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>highlight_date</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>漲跌BYN天</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>增縮BYN天</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>漲跌BYN天Diff</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>增縮BYN天Diff</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>盤後量</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>成交量</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>MA5_%</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>均價_%</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>均價long_%</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>MA_short</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>MA_long</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>MA_longlong</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>MACD_%</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>MACD</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>MACD-SL</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>%K</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>%D</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>VPC_MA_%</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>VPC_break</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Volume_MA_short</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Volume_MA_long</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>Volume_Oscillator</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>volume_threshold</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>Volume_Price_Change_sum</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>highlight_enddate</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>Type0</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>Type1</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>Type2</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>Full_Summary</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>textdesc</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>盤後量</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>成交量</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>MA5_%</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>均價_%</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>均價long_%</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>MA_short</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>MA_long</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>MA_longlong</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>MACD_%</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>MACD</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>MACD-SL</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>%K</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>%D</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>VPC_MA_%</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>VPC_break</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>Volume_MA_short</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>Volume_MA_long</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>Volume_Oscillator</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>volume_threshold</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>Volume_Price_Change_sum</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>highlight_date</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>highlight_enddate</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>Type0</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>Type1</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>Type2</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>Full_Summary</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
